--- a/VerveStacks_CAN/vt_vervestacks_CAN_v1.xlsx
+++ b/VerveStacks_CAN/vt_vervestacks_CAN_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CAN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{3F85BEA0-B6B6-4AAB-80B0-64B47AAC260F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{EE619EB1-217F-4683-81A6-A4F7253F5E9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{E4CA058D-914D-4BD4-8A9A-98B2C6AC6721}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{D5EF87A8-3516-423B-8D30-F5D29867A841}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="2" r:id="rId1"/>
@@ -3500,7 +3500,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{3516CD7D-47C1-47A0-A6A8-6E443645186A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B55D6E3F-16C2-4F68-A394-1BE30CE79583}">
   <dimension ref="B9:T267"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -17252,7 +17252,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AB8349D6-4361-4633-94FA-D9A3AD4F5A92}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5CF8FA2-34C0-4196-B0C3-1D5EEA9FE8D7}">
   <dimension ref="B9:T540"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_CAN/vt_vervestacks_CAN_v1.xlsx
+++ b/VerveStacks_CAN/vt_vervestacks_CAN_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CAN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{EE619EB1-217F-4683-81A6-A4F7253F5E9E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{39D3487E-8607-4068-AB15-9C2F6ED73906}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{D5EF87A8-3516-423B-8D30-F5D29867A841}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{ADF8CFEA-8958-4745-8204-9D856253959F}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="2" r:id="rId1"/>
@@ -3500,7 +3500,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B55D6E3F-16C2-4F68-A394-1BE30CE79583}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC3D19AF-45F1-42F6-B121-441607732733}">
   <dimension ref="B9:T267"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -17252,7 +17252,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F5CF8FA2-34C0-4196-B0C3-1D5EEA9FE8D7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62E70F6F-4254-4E54-9828-61F9CADD0689}">
   <dimension ref="B9:T540"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_CAN/vt_vervestacks_CAN_v1.xlsx
+++ b/VerveStacks_CAN/vt_vervestacks_CAN_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CAN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{39D3487E-8607-4068-AB15-9C2F6ED73906}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{948A05DA-2FB4-4F7B-90A2-07DA9213DB79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{ADF8CFEA-8958-4745-8204-9D856253959F}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{D94B3D0E-1EB3-44AF-B8C3-4C8DAD6D921C}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="2" r:id="rId1"/>
@@ -3500,7 +3500,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DC3D19AF-45F1-42F6-B121-441607732733}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A3EB395-5A88-4A68-A89A-0FF71D41ABA5}">
   <dimension ref="B9:T267"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -17252,7 +17252,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{62E70F6F-4254-4E54-9828-61F9CADD0689}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97442BFB-88A1-46EF-A05F-2B6A9C781958}">
   <dimension ref="B9:T540"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_CAN/vt_vervestacks_CAN_v1.xlsx
+++ b/VerveStacks_CAN/vt_vervestacks_CAN_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CAN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{948A05DA-2FB4-4F7B-90A2-07DA9213DB79}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E2F5D4AB-230D-491A-B326-B3DBD4CBE852}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{D94B3D0E-1EB3-44AF-B8C3-4C8DAD6D921C}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{5E0C1772-FC81-49B7-ACEA-2AD5A10E68F4}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="2" r:id="rId1"/>
@@ -3500,7 +3500,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{2A3EB395-5A88-4A68-A89A-0FF71D41ABA5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E751B593-7EB9-40ED-9056-CAF5E8629FA7}">
   <dimension ref="B9:T267"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -17252,7 +17252,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{97442BFB-88A1-46EF-A05F-2B6A9C781958}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{85A5842E-1CB3-4940-BEE2-FBB6F6725233}">
   <dimension ref="B9:T540"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>

--- a/VerveStacks_CAN/vt_vervestacks_CAN_v1.xlsx
+++ b/VerveStacks_CAN/vt_vervestacks_CAN_v1.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Veda\Veda\Veda_models\vervestacks_models\VerveStacks_CAN\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{8A82F343-F2ED-4300-81FD-1D4B73A40015}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{4986F99C-975A-4AA4-8E73-3C2E34A723F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{F02E6BE6-37EF-47DB-BC54-8248FF62070A}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" xr2:uid="{E5F37C76-740D-4FE2-B079-1EFCB87B96F7}"/>
   </bookViews>
   <sheets>
     <sheet name="ccs_retrofits" sheetId="2" r:id="rId1"/>
@@ -2894,7 +2894,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A821B00E-E43B-4245-850B-CD5DA04B6E6A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FA655946-288C-45E2-9511-8118ACEBDA6A}">
   <dimension ref="B9:T148"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
@@ -10360,7 +10360,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{60A7F2FC-A154-4D33-B8F2-0148C7E3CC5A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{ABC2C8DA-FEC8-45C0-BAE1-7F7D9DFE9232}">
   <dimension ref="B9:T421"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <sheetData>
